--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486834_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486834_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7013</v>
+        <v>3.6323</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1144</v>
+        <v>3.1695</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5869</v>
+        <v>0.4628</v>
       </c>
       <c r="G2" t="n">
         <v>2.3276</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4413</v>
+        <v>-0.5103</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0548</v>
+        <v>0.11</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4961</v>
+        <v>-0.6203</v>
       </c>
       <c r="V2" t="n">
         <v>0.6565</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>M. SOLE MOURATAY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7417</v>
+        <v>0.5095</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6777</v>
+        <v>2.8212</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-2.3117</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5982</v>
+        <v>-1.7732</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.351</v>
+        <v>1.4007</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7528</v>
+        <v>-3.174</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9683</v>
+        <v>2.6216</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2358</v>
+        <v>2.574</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7325</v>
+        <v>0.0476</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5665</v>
+        <v>-4.3948</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5868</v>
+        <v>-1.1733</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0203</v>
+        <v>-3.2215</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7723</v>
+        <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8187</v>
+        <v>-0.138</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6748</v>
+        <v>0.2888</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1438</v>
+        <v>-0.4268</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2856</v>
+        <v>1.8415</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SOLE MOURATAY</t>
+          <t>R. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5248</v>
+        <v>0.1379</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9177</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3929</v>
+        <v>0.1379</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7732</v>
+        <v>0.1379</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4007</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.174</v>
+        <v>0.1379</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6216</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2.574</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.3948</v>
+        <v>0.1379</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1733</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.2215</v>
+        <v>0.1379</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8773</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3853</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.492</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. PEREZ RUIZ</t>
+          <t>V. DEL GROSSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1379</v>
+        <v>-0.1174</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1379</v>
+        <v>-0.8074</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1379</v>
+        <v>-0.0068</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.6691</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1379</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.6696</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.359</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6895</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1379</v>
+        <v>-0.6764</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.6899</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1379</v>
+        <v>0.0135</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.0759</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0205</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.0964</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. DEL GROSSO</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7145</v>
+        <v>-0.2081</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1177</v>
+        <v>0.9265</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-1.1346</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0068</v>
+        <v>-0.5982</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6691</v>
+        <v>-1.351</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.7528</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6696</v>
+        <v>0.9683</v>
       </c>
       <c r="K6" t="n">
-        <v>1.359</v>
+        <v>0.2358</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6895</v>
+        <v>0.7325</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6764</v>
+        <v>-1.5665</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6899</v>
+        <v>-1.5868</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0135</v>
+        <v>0.0203</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.673</v>
+        <v>0.8688</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5518</v>
+        <v>0.9236</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1212</v>
+        <v>-0.0548</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.273</v>
+        <v>-0.2993</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7562</v>
+        <v>2.4319</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0291</v>
+        <v>-2.7312</v>
       </c>
       <c r="G7" t="n">
         <v>-2.1831</v>
@@ -1000,13 +1000,13 @@
         <v>2.51</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.2564</v>
+        <v>-1.2827</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6625</v>
+        <v>0.0132</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.5939</v>
+        <v>-1.2959</v>
       </c>
       <c r="V7" t="n">
         <v>0.6565</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2273</v>
+        <v>-3.7657</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4721</v>
+        <v>-1.6764</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.6994</v>
+        <v>-2.0892</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8599</v>
+        <v>-4.3117</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0136</v>
+        <v>-1.2757</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8463</v>
+        <v>-3.0361</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6108</v>
+        <v>-0.5039</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3666</v>
+        <v>0.1042</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2442</v>
+        <v>-0.6081</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.4706</v>
+        <v>-3.8079</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3802</v>
+        <v>-1.3799</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.0904</v>
+        <v>-2.428</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9547</v>
+        <v>-0.6896</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8268</v>
+        <v>-0.2072</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.7814</v>
+        <v>-0.4824</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5712</v>
+        <v>0.6565</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5712</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6207</v>
+        <v>-4.6174</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4073</v>
+        <v>-0.1414</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2134</v>
+        <v>-4.4759</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.3117</v>
+        <v>-3.8599</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2757</v>
+        <v>-1.0136</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.0361</v>
+        <v>-2.8463</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5039</v>
+        <v>0.6108</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1042</v>
+        <v>0.3666</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6081</v>
+        <v>0.2442</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.8079</v>
+        <v>-4.4706</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3799</v>
+        <v>-1.3802</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.428</v>
+        <v>-3.0904</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5447</v>
+        <v>-1.3448</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9381</v>
+        <v>0.2132</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6066</v>
+        <v>-1.5579</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6565</v>
+        <v>-0.5712</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6565</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.6163</v>
+        <v>-6.586</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.699</v>
+        <v>-2.0163</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.9173</v>
+        <v>-4.5697</v>
       </c>
       <c r="G10" t="n">
         <v>-6.5415</v>
@@ -1234,13 +1234,13 @@
         <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.5269</v>
+        <v>-1.4966</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6988</v>
+        <v>-1.3511</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2856</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.025700000000001</v>
+        <v>-7.2299</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.291</v>
+        <v>-2.7187</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.7347</v>
+        <v>-4.5112</v>
       </c>
       <c r="G11" t="n">
         <v>-2.637</v>
@@ -1312,13 +1312,13 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2302</v>
+        <v>-0.4344</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5518</v>
+        <v>0.0205</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6784</v>
+        <v>-0.4549</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8415</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.3718</v>
+        <v>-18.5441</v>
       </c>
       <c r="E12" t="n">
-        <v>2.658499999999999</v>
+        <v>3.486299999999999</v>
       </c>
       <c r="F12" t="n">
         <v>-22.0302</v>
@@ -1381,7 +1381,7 @@
         <v>-15.3843</v>
       </c>
       <c r="P12" t="n">
-        <v>5.792299999999999</v>
+        <v>5.792300000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-7.7232</v>
@@ -1390,13 +1390,13 @@
         <v>13.5154</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.9312</v>
+        <v>-5.103499999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4094</v>
+        <v>1.2372</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.340599999999999</v>
+        <v>-6.3405</v>
       </c>
       <c r="V12" t="n">
         <v>0.2132999999999998</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.279</v>
+        <v>10.9128</v>
       </c>
       <c r="E13" t="n">
-        <v>7.7151</v>
+        <v>11.0386</v>
       </c>
       <c r="F13" t="n">
-        <v>1.564</v>
+        <v>-0.1259</v>
       </c>
       <c r="G13" t="n">
-        <v>4.0244</v>
+        <v>9.023199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8143</v>
+        <v>3.1861</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2101</v>
+        <v>5.8371</v>
       </c>
       <c r="J13" t="n">
-        <v>5.6268</v>
+        <v>10.4874</v>
       </c>
       <c r="K13" t="n">
-        <v>5.0571</v>
+        <v>3.6012</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5697</v>
+        <v>6.8861</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6023</v>
+        <v>-1.4641</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2428</v>
+        <v>-0.4151</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3596</v>
+        <v>-1.049</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>8.247299999999999</v>
+        <v>0.8895</v>
       </c>
       <c r="T13" t="n">
-        <v>6.0118</v>
+        <v>0.9028</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2355</v>
+        <v>-0.0133</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.6412</v>
+        <v>0.6138</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.0273</v>
+        <v>0.6138</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.1736</v>
+        <v>9.7387</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1078</v>
+        <v>9.6921</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9342</v>
+        <v>0.0466</v>
       </c>
       <c r="G14" t="n">
-        <v>9.023199999999999</v>
+        <v>7.2046</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1861</v>
+        <v>0.8612</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8371</v>
+        <v>6.3434</v>
       </c>
       <c r="J14" t="n">
-        <v>10.4874</v>
+        <v>7.9171</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6012</v>
+        <v>1.4832</v>
       </c>
       <c r="L14" t="n">
-        <v>6.8861</v>
+        <v>6.4339</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4641</v>
+        <v>-0.7126</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4151</v>
+        <v>-0.622</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.049</v>
+        <v>-0.0905</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3862</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8496</v>
+        <v>0.7932</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.028</v>
+        <v>0.6132</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8216</v>
+        <v>0.1799</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6138</v>
+        <v>2.1271</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6138</v>
+        <v>2.1271</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.5044</v>
+        <v>4.659</v>
       </c>
       <c r="E15" t="n">
-        <v>8.9682</v>
+        <v>4.1987</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4638</v>
+        <v>0.4603</v>
       </c>
       <c r="G15" t="n">
-        <v>7.2046</v>
+        <v>4.0244</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8612</v>
+        <v>3.8143</v>
       </c>
       <c r="I15" t="n">
-        <v>6.3434</v>
+        <v>0.2101</v>
       </c>
       <c r="J15" t="n">
-        <v>7.9171</v>
+        <v>5.6268</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4832</v>
+        <v>5.0571</v>
       </c>
       <c r="L15" t="n">
-        <v>6.4339</v>
+        <v>0.5697</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7126</v>
+        <v>-1.6023</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.622</v>
+        <v>-1.2428</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0905</v>
+        <v>-0.3596</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3862</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4412</v>
+        <v>3.6272</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1107</v>
+        <v>2.4954</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3304</v>
+        <v>1.1318</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1271</v>
+        <v>-1.6412</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1271</v>
+        <v>-1.0273</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2045</v>
+        <v>1.0554</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2018</v>
+        <v>0.1534</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0028</v>
+        <v>0.902</v>
       </c>
       <c r="G16" t="n">
-        <v>3.753</v>
+        <v>-0.7711</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3235</v>
+        <v>-2.0212</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4295</v>
+        <v>1.2501</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2585</v>
+        <v>-0.114</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4626</v>
+        <v>-1.0545</v>
       </c>
       <c r="L16" t="n">
-        <v>3.7958</v>
+        <v>0.9405</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.6571</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1391</v>
+        <v>-0.9667</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3663</v>
+        <v>0.3096</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.2823</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.8616</v>
+        <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3904</v>
+        <v>1.0275</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4613</v>
+        <v>1.0132</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.0144</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6565</v>
+        <v>1.1851</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6565</v>
+        <v>1.1851</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. RODRÍGUEZ GONZÁLEZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0843</v>
+        <v>0.9866</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0207</v>
+        <v>0.9949</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1049</v>
+        <v>-0.0083</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0205</v>
+        <v>3.753</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1174</v>
+        <v>0.3235</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1379</v>
+        <v>3.4295</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0207</v>
+        <v>4.2585</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0207</v>
+        <v>0.4626</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.7958</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0002</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1381</v>
+        <v>-0.1391</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1379</v>
+        <v>-0.3663</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-3.2823</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1048</v>
+        <v>1.1724</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.2545</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1048</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>I. RODRÍGUEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0878</v>
+        <v>-0.0346</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7774</v>
+        <v>0.0207</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6896</v>
+        <v>-0.0553</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7711</v>
+        <v>0.0205</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0212</v>
+        <v>-0.1174</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2501</v>
+        <v>0.1379</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.114</v>
+        <v>0.0207</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0545</v>
+        <v>0.0207</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9405</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6571</v>
+        <v>-0.0002</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9667</v>
+        <v>-0.1381</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3096</v>
+        <v>0.1379</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5446</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1156</v>
+        <v>-0.0551</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0824</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.198</v>
+        <v>-0.0551</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1851</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1851</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1593</v>
+        <v>-0.9525</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0555</v>
+        <v>-0.8487</v>
       </c>
       <c r="F20" t="n">
         <v>-0.1038</v>
@@ -2014,10 +2014,10 @@
         <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1654</v>
+        <v>0.0414</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1655</v>
+        <v>0.0413</v>
       </c>
       <c r="U20" t="n">
         <v>0.0001</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.69</v>
+        <v>-2.0198</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3428</v>
+        <v>-1.7222</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3472</v>
+        <v>-0.2975</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0061</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.877</v>
+        <v>-0.2068</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4691</v>
+        <v>0.1514</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4079</v>
+        <v>-0.3582</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9477</v>
+        <v>-3.4636</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8075</v>
+        <v>-1.4973</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1402</v>
+        <v>-1.9663</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1258</v>
@@ -2170,13 +2170,13 @@
         <v>0.1931</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0149</v>
+        <v>-0.5308</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4415</v>
+        <v>-0.1312</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5735</v>
+        <v>-0.3997</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,25 +2203,25 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>19.3716</v>
+        <v>20.0612</v>
       </c>
       <c r="E23" t="n">
-        <v>22.0304</v>
+        <v>22.0302</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6585</v>
+        <v>-1.969</v>
       </c>
       <c r="G23" t="n">
         <v>19.446</v>
       </c>
       <c r="H23" t="n">
-        <v>4.480400000000001</v>
+        <v>4.480399999999999</v>
       </c>
       <c r="I23" t="n">
         <v>14.9655</v>
       </c>
       <c r="J23" t="n">
-        <v>25.7352</v>
+        <v>25.73519999999999</v>
       </c>
       <c r="K23" t="n">
         <v>10.3507</v>
@@ -2236,7 +2236,7 @@
         <v>-5.8703</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4187999999999997</v>
+        <v>-0.4188000000000002</v>
       </c>
       <c r="P23" t="n">
         <v>-5.7923</v>
@@ -2248,16 +2248,16 @@
         <v>7.7229</v>
       </c>
       <c r="S23" t="n">
-        <v>5.9313</v>
+        <v>6.6206</v>
       </c>
       <c r="T23" t="n">
-        <v>6.3407</v>
+        <v>6.3406</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4095</v>
+        <v>0.2798999999999998</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2132000000000001</v>
+        <v>-0.2132000000000003</v>
       </c>
       <c r="W23" t="n">
         <v>3.4699</v>
